--- a/product_search/product_list.xlsx
+++ b/product_search/product_list.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Imdia\Desktop\product_search\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Imdia\Desktop\벨루트\벨루트_상세\bellroute-image-hosting\product_search\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -74,23 +74,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>est</t>
-    </r>
+    <t>https://bellroute.co.kr/product/11%ED%95%A0%EC%9D%B8-%EB%B2%8C%EB%A3%AC%ED%95%8F-%EC%BB%A4%EB%B8%8C%EB%93%9C-%EC%A1%B0%EA%B1%B0%ED%8C%AC%EC%B8%A0-5color/19/category/1/display/2/?icid=MAIN.product_listmain_1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://bellroute.co.kr/product/11%ED%95%A0%EC%9D%B8-%EB%B2%8C%EB%A3%AC%ED%95%8F-%EC%BB%A4%EB%B8%8C%EB%93%9C-%EC%A1%B0%EA%B1%B0%ED%8C%AC%EC%B8%A0-5color/19/category/1/display/2/?icid=MAIN.product_listmain_1</t>
+    <t>커브드 사이드핀턱 벌룬팬츠 (6color)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -686,7 +674,7 @@
   <sheetFormatPr defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14.3984375" style="1"/>
-    <col min="2" max="2" width="14.3984375" style="2"/>
+    <col min="2" max="2" width="32.69921875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="230.09765625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.3984375" style="2"/>
   </cols>
@@ -707,10 +695,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/product_search/product_list.xlsx
+++ b/product_search/product_list.xlsx
@@ -12,7 +12,16 @@
     <workbookView xWindow="7392" yWindow="528" windowWidth="21360" windowHeight="15480" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="상의" sheetId="1" r:id="rId1"/>
+    <sheet name="하의" sheetId="2" r:id="rId2"/>
+    <sheet name="아우터" sheetId="3" r:id="rId3"/>
+    <sheet name="트레이닝" sheetId="10" r:id="rId4"/>
+    <sheet name="세트" sheetId="4" r:id="rId5"/>
+    <sheet name="U상의" sheetId="5" r:id="rId6"/>
+    <sheet name="U하의" sheetId="6" r:id="rId7"/>
+    <sheet name="U아우터" sheetId="7" r:id="rId8"/>
+    <sheet name="U트레이닝" sheetId="11" r:id="rId9"/>
+    <sheet name="U세트" sheetId="8" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -32,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="129">
   <si>
     <t>자체상품코드</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -58,27 +67,443 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>001</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://bellroute.co.kr/product/11%ED%95%A0%EC%9D%B8-%EB%B2%8C%EB%A3%AC%ED%95%8F-%EC%BB%A4%EB%B8%8C%EB%93%9C-%EC%A1%B0%EA%B1%B0%ED%8C%AC%EC%B8%A0-5color/19/category/1/display/2/?icid=MAIN.product_listmain_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>커브드 사이드핀턱 벌룬팬츠 (6color)</t>
+    <t>와이드핏 워싱 데님팬츠 (5Color)</t>
+  </si>
+  <si>
+    <t>MBT0001</t>
+  </si>
+  <si>
+    <t>세미와이드핏 슬랙스 (5Color)</t>
+  </si>
+  <si>
+    <t>MBT0002</t>
+  </si>
+  <si>
+    <t>벌룬핏 커브드 데님팬츠 (4Color)</t>
+  </si>
+  <si>
+    <t>MBT0003</t>
+  </si>
+  <si>
+    <t>MBT0004</t>
+  </si>
+  <si>
+    <t>테이퍼드핏 슬랙스 (4Color)</t>
+  </si>
+  <si>
+    <t>와이드핏 무지 데님팬츠 (7Color)</t>
+  </si>
+  <si>
+    <t>MBT0005</t>
+  </si>
+  <si>
+    <t>루즈핏 생지데님자켓 (2Color)</t>
+  </si>
+  <si>
+    <t>MOT0001</t>
+  </si>
+  <si>
+    <t>MBT0006</t>
+  </si>
+  <si>
+    <t>벌룬핏 코듀로이 카고팬츠 (3Color)</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOT0002</t>
+  </si>
+  <si>
+    <t>크롭 하이넥 웰론패딩 (2Color)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UTR0001</t>
+  </si>
+  <si>
+    <t>[1+1할인] 벌룬핏 커브드 조거팬츠 (5Color)</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MTP0001</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여름 오버핏 린넨셔츠 (5Color)</t>
+  </si>
+  <si>
+    <t>[1+1 할인] 커브드 사이드핀턱 벌룬팬츠 (6color)</t>
+  </si>
+  <si>
+    <t>UTR0002</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1+1 할인] 드롭숄더 무지 오버핏 맨투맨 (7Color)</t>
+  </si>
+  <si>
+    <t>UTP0001</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UOT0001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1+1 할인] 드롭숄더 무지 오버핏 후드집업 (7color)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UTP0002</t>
+  </si>
+  <si>
+    <t>[1+1 할인] 오버핏 드롭숄더 후드티셔츠 (7Color)</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>슬림핏 워싱 데님스키니 (7Color)</t>
+  </si>
+  <si>
+    <t>MBT0007</t>
+  </si>
+  <si>
+    <t>MBT0008</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=27</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레어핏 부츠컷 데님팬츠 (3Color)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1+1 할인] 머슬핏 쿨링 반팔티셔츠 (6Color)</t>
+  </si>
+  <si>
+    <t>MTP0002</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=28</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>루즈핏 후드 바람막이자켓 (2Color)</t>
+  </si>
+  <si>
+    <t>MOT0003</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UTR0003</t>
+  </si>
+  <si>
+    <t>[1+1 할인] 박시핏 사이드핀턱 버뮤다팬츠 (4Color)</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MTR0001</t>
+  </si>
+  <si>
+    <t>플레어핏 부츠컷팬츠 (2Color)</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UTR0004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1+1 할인] 카펜더 버뮤다팬츠 (3Color)</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UTR0005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1+1 할인] 쿨링 벌룬핏 팬츠 (4Color)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쿨링 세미와이드핏 데님팬츠 (4Color)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MBT0009</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=34</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쿨링 생지데님 세미와이드핏 팬츠 (2Color)</t>
+  </si>
+  <si>
+    <t>MBT0010</t>
+  </si>
+  <si>
+    <t>UTR0006</t>
+  </si>
+  <si>
+    <t>파라슈트 와이드핏 나일론 팬츠 (4Color)</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=36</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쿨링 세미와이드핏 슬랙스 (4Color)</t>
+  </si>
+  <si>
+    <t>MBT0011</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=37</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쿨링 테이퍼드핏 슬랙스 (4Color)</t>
+  </si>
+  <si>
+    <t>MBT0012</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=38</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MBT0013</t>
+  </si>
+  <si>
+    <t>데님버뮤다 와이드핏 반바지 (5Color)</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=39</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UTP0003</t>
+  </si>
+  <si>
+    <t>오버핏 린넨셔츠 소라색셔츠 (6Color)</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=41</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UST0001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아노락세트 바스락셋업 여름 트레이닝 (4Color)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UTR0007</t>
+  </si>
+  <si>
+    <t>[1+1 할인] 카고 버뮤다팬츠 (4Color)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=42</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>루즈핏 꽈배기 카라반팔니트 (8Color)</t>
+  </si>
+  <si>
+    <t>UTP0004</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=43</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오버핏 어깨 넓어보이는 절개 반팔티 (6Color)</t>
+  </si>
+  <si>
+    <t>MTP0003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=44</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UTR0008</t>
+  </si>
+  <si>
+    <t>사이드핀턱 커브드핏 파라슈트팬츠 (4Color)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MST0001</t>
+  </si>
+  <si>
+    <t>머슬핏 꽈배기니트 반팔셋업 (4Color)</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=46</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데님워싱 커브드핏 벌룬팬츠 (5Color)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MBT0014</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=48</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머슬핏 오픈카라 스트라이프 니트티셔츠 (4Color)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MTP0004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=49</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>헨리넥 머슬핏 반팔니트셋업 (4Color)</t>
+  </si>
+  <si>
+    <t>MST0002</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MTP0005</t>
+  </si>
+  <si>
+    <t>[1+1 할인] 헨리넥 머슬핏 골지반팔티셔츠 (3Color)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=51</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MTP0006</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=52</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남자폴라니트 목티 반목폴라 반폴라 모크넥니트 긴팔티셔츠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=53</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOT0004</t>
+  </si>
+  <si>
+    <t>크롭핏 하이넥 블루종집업 (3Color)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MTP0007</t>
+  </si>
+  <si>
+    <t>[1+1 할인] 머슬핏 반목폴라 긴팔티셔츠 (8Color)</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=55</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -114,12 +539,18 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -139,7 +570,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -157,6 +588,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -670,12 +1110,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="14.3984375" style="1"/>
-    <col min="2" max="2" width="32.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="230.09765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="56.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.59765625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.3984375" style="2"/>
   </cols>
   <sheetData>
@@ -692,13 +1132,127 @@
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>4</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId2"/>
+    <hyperlink ref="C4" r:id="rId3"/>
+    <hyperlink ref="C5" r:id="rId4"/>
+    <hyperlink ref="C6" r:id="rId5"/>
+    <hyperlink ref="C7" r:id="rId6"/>
+    <hyperlink ref="C8" r:id="rId7"/>
+  </hyperlinks>
+  <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape" r:id="rId8"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="8.796875" style="2"/>
+    <col min="2" max="2" width="41.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.69921875" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -706,7 +1260,627 @@
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1"/>
   </hyperlinks>
-  <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="12.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.69921875" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A14" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A15" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId2"/>
+    <hyperlink ref="C4" r:id="rId3"/>
+    <hyperlink ref="C5" r:id="rId4"/>
+    <hyperlink ref="C6" r:id="rId5"/>
+    <hyperlink ref="C7" r:id="rId6"/>
+    <hyperlink ref="C8" r:id="rId7"/>
+    <hyperlink ref="C9" r:id="rId8"/>
+    <hyperlink ref="C10" r:id="rId9"/>
+    <hyperlink ref="C11" r:id="rId10"/>
+    <hyperlink ref="C12" r:id="rId11"/>
+    <hyperlink ref="C13" r:id="rId12"/>
+    <hyperlink ref="C14" r:id="rId13"/>
+    <hyperlink ref="C15" r:id="rId14"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="12.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.69921875" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId2"/>
+    <hyperlink ref="C4" r:id="rId3"/>
+    <hyperlink ref="C5" r:id="rId4"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="12.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.69921875" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="12.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.8984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.69921875" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="12.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.69921875" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId2"/>
+    <hyperlink ref="C4" r:id="rId3"/>
+    <hyperlink ref="C5" r:id="rId4"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="12.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.69921875" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="12.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.69921875" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId2"/>
+    <hyperlink ref="C4" r:id="rId3"/>
+    <hyperlink ref="C5" r:id="rId4"/>
+    <hyperlink ref="C6" r:id="rId5"/>
+    <hyperlink ref="C7" r:id="rId6"/>
+    <hyperlink ref="C8" r:id="rId7"/>
+    <hyperlink ref="C9" r:id="rId8"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/product_search/product_list.xlsx
+++ b/product_search/product_list.xlsx
@@ -24,6 +24,22 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment authorId="0" ref="A2">
+      <text>
+        <t xml:space="preserve">남녀공용이지만, 여자상품으로 여자코드사용
+======</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="137">
   <si>
@@ -31,6 +47,33 @@
   </si>
   <si>
     <t>상품명</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Malgun Gothic"/>
+        <color rgb="FF000000"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t xml:space="preserve">상세페이지 </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="맑은 고딕"/>
+        <color rgb="FF000000"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t>URL</t>
+    </r>
+  </si>
+  <si>
+    <t>MTP0001</t>
+  </si>
+  <si>
+    <t>여름 오버핏 린넨셔츠 (5Color)</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=21</t>
   </si>
   <si>
     <r>
@@ -69,6 +112,24 @@
     </r>
   </si>
   <si>
+    <t>MOT0001</t>
+  </si>
+  <si>
+    <t>루즈핏 생지데님자켓 (2Color)</t>
+  </si>
+  <si>
+    <t>WBT0001</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=16</t>
+  </si>
+  <si>
+    <t>와이드핏 워싱 데님팬츠 (5Color)</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=11</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <rFont val="Malgun Gothic"/>
@@ -90,64 +151,10 @@
     <t>MTR0001</t>
   </si>
   <si>
-    <t>MTP0001</t>
-  </si>
-  <si>
-    <t>여름 오버핏 린넨셔츠 (5Color)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Malgun Gothic"/>
-        <color rgb="FF000000"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve">상세페이지 </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color rgb="FF000000"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>URL</t>
-    </r>
-  </si>
-  <si>
     <t>플레어핏 부츠컷팬츠 (2Color)</t>
   </si>
   <si>
-    <t>MOT0001</t>
-  </si>
-  <si>
-    <t>MBT0001</t>
-  </si>
-  <si>
-    <t>https://bellroute.cafe24.com/product/detail.html?product_no=21</t>
-  </si>
-  <si>
     <t>https://bellroute.cafe24.com/product/detail.html?product_no=31</t>
-  </si>
-  <si>
-    <t>와이드핏 워싱 데님팬츠 (5Color)</t>
-  </si>
-  <si>
-    <t>루즈핏 생지데님자켓 (2Color)</t>
-  </si>
-  <si>
-    <t>https://bellroute.cafe24.com/product/detail.html?product_no=11</t>
-  </si>
-  <si>
-    <t>https://bellroute.cafe24.com/product/detail.html?product_no=16</t>
-  </si>
-  <si>
-    <t>MBT0002</t>
-  </si>
-  <si>
-    <t>세미와이드핏 슬랙스 (5Color)</t>
-  </si>
-  <si>
-    <t>https://bellroute.cafe24.com/product/detail.html?product_no=12</t>
   </si>
   <si>
     <t>MTP0002</t>
@@ -162,37 +169,37 @@
     <t>MOT0002</t>
   </si>
   <si>
+    <t>크롭 하이넥 웰론패딩 (2Color)</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=18</t>
+  </si>
+  <si>
+    <t>MBT0002</t>
+  </si>
+  <si>
+    <t>세미와이드핏 슬랙스 (5Color)</t>
+  </si>
+  <si>
     <t>MTP0003</t>
   </si>
   <si>
     <t>오버핏 어깨 넓어보이는 절개 반팔티 (6Color)</t>
   </si>
   <si>
-    <t>MBT0003</t>
-  </si>
-  <si>
-    <t>크롭 하이넥 웰론패딩 (2Color)</t>
-  </si>
-  <si>
-    <t>벌룬핏 커브드 데님팬츠 (4Color)</t>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=12</t>
   </si>
   <si>
     <t>https://bellroute.cafe24.com/product/detail.html?product_no=44</t>
   </si>
   <si>
-    <t>https://bellroute.cafe24.com/product/detail.html?product_no=13</t>
+    <t>MOT0003</t>
   </si>
   <si>
-    <t>https://bellroute.cafe24.com/product/detail.html?product_no=18</t>
+    <t>루즈핏 후드 바람막이자켓 (2Color)</t>
   </si>
   <si>
-    <t>MBT0004</t>
-  </si>
-  <si>
-    <t>테이퍼드핏 슬랙스 (4Color)</t>
-  </si>
-  <si>
-    <t>https://bellroute.cafe24.com/product/detail.html?product_no=14</t>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=29</t>
   </si>
   <si>
     <t>MTP0004</t>
@@ -204,22 +211,13 @@
     <t>https://bellroute.cafe24.com/product/detail.html?product_no=49</t>
   </si>
   <si>
-    <t>MOT0003</t>
+    <t>MBT0003</t>
   </si>
   <si>
-    <t>루즈핏 후드 바람막이자켓 (2Color)</t>
+    <t>벌룬핏 커브드 데님팬츠 (4Color)</t>
   </si>
   <si>
-    <t>https://bellroute.cafe24.com/product/detail.html?product_no=29</t>
-  </si>
-  <si>
-    <t>MBT0005</t>
-  </si>
-  <si>
-    <t>와이드핏 무지 데님팬츠 (7Color)</t>
-  </si>
-  <si>
-    <t>https://bellroute.cafe24.com/product/detail.html?product_no=15</t>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=13</t>
   </si>
   <si>
     <t>MTP0005</t>
@@ -240,6 +238,42 @@
     <t>https://bellroute.cafe24.com/product/detail.html?product_no=53</t>
   </si>
   <si>
+    <t>MBT0004</t>
+  </si>
+  <si>
+    <t>MTP0006</t>
+  </si>
+  <si>
+    <t>남자폴라니트 목티 반목폴라 반폴라 모크넥니트 긴팔티셔츠</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=52</t>
+  </si>
+  <si>
+    <t>테이퍼드핏 슬랙스 (4Color)</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=14</t>
+  </si>
+  <si>
+    <t>MTP0007</t>
+  </si>
+  <si>
+    <t>[1+1 할인] 머슬핏 반목폴라 긴팔티셔츠 (8Color)</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=55</t>
+  </si>
+  <si>
+    <t>MBT0005</t>
+  </si>
+  <si>
+    <t>와이드핏 무지 데님팬츠 (7Color)</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=15</t>
+  </si>
+  <si>
     <t>MBT0006</t>
   </si>
   <si>
@@ -249,19 +283,10 @@
     <t>https://bellroute.cafe24.com/product/detail.html?product_no=17</t>
   </si>
   <si>
-    <t>MTP0006</t>
-  </si>
-  <si>
     <t>MBT0007</t>
   </si>
   <si>
-    <t>남자폴라니트 목티 반목폴라 반폴라 모크넥니트 긴팔티셔츠</t>
-  </si>
-  <si>
     <t>슬림핏 워싱 데님스키니 (7Color)</t>
-  </si>
-  <si>
-    <t>https://bellroute.cafe24.com/product/detail.html?product_no=52</t>
   </si>
   <si>
     <t>https://bellroute.cafe24.com/product/detail.html?product_no=26</t>
@@ -274,15 +299,6 @@
   </si>
   <si>
     <t>https://bellroute.cafe24.com/product/detail.html?product_no=27</t>
-  </si>
-  <si>
-    <t>MTP0007</t>
-  </si>
-  <si>
-    <t>[1+1 할인] 머슬핏 반목폴라 긴팔티셔츠 (8Color)</t>
-  </si>
-  <si>
-    <t>https://bellroute.cafe24.com/product/detail.html?product_no=55</t>
   </si>
   <si>
     <t>MBT0009</t>
@@ -360,12 +376,6 @@
     <t>MST0001</t>
   </si>
   <si>
-    <t>머슬핏 꽈배기니트 반팔셋업 (4Color)</t>
-  </si>
-  <si>
-    <t>https://bellroute.cafe24.com/product/detail.html?product_no=46</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <rFont val="Malgun Gothic"/>
@@ -384,6 +394,12 @@
     </r>
   </si>
   <si>
+    <t>머슬핏 꽈배기니트 반팔셋업 (4Color)</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=46</t>
+  </si>
+  <si>
     <t>UTP0001</t>
   </si>
   <si>
@@ -393,6 +409,15 @@
     <t>https://bellroute.cafe24.com/product/detail.html?product_no=23</t>
   </si>
   <si>
+    <t>UTP0002</t>
+  </si>
+  <si>
+    <t>[1+1 할인] 오버핏 드롭숄더 후드티셔츠 (7Color)</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=25</t>
+  </si>
+  <si>
     <t>MST0002</t>
   </si>
   <si>
@@ -400,15 +425,6 @@
   </si>
   <si>
     <t>https://bellroute.cafe24.com/product/detail.html?product_no=50</t>
-  </si>
-  <si>
-    <t>UTP0002</t>
-  </si>
-  <si>
-    <t>[1+1 할인] 오버핏 드롭숄더 후드티셔츠 (7Color)</t>
-  </si>
-  <si>
-    <t>https://bellroute.cafe24.com/product/detail.html?product_no=25</t>
   </si>
   <si>
     <t>UTP0003</t>
@@ -472,33 +488,6 @@
       </rPr>
       <t>URL</t>
     </r>
-  </si>
-  <si>
-    <t>UST0001</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Malgun Gothic"/>
-        <color rgb="FF000000"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve">상세페이지 </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="맑은 고딕"/>
-        <color rgb="FF000000"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>URL</t>
-    </r>
-  </si>
-  <si>
-    <t>아노락세트 바스락셋업 여름 트레이닝 (4Color)</t>
-  </si>
-  <si>
-    <t>https://bellroute.cafe24.com/product/detail.html?product_no=41</t>
   </si>
   <si>
     <t>UTR0001</t>
@@ -572,6 +561,33 @@
   <si>
     <t>https://bellroute.cafe24.com/product/detail.html?product_no=45</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Malgun Gothic"/>
+        <color rgb="FF000000"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t xml:space="preserve">상세페이지 </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="맑은 고딕"/>
+        <color rgb="FF000000"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t>URL</t>
+    </r>
+  </si>
+  <si>
+    <t>UST0001</t>
+  </si>
+  <si>
+    <t>아노락세트 바스락셋업 여름 트레이닝 (4Color)</t>
+  </si>
+  <si>
+    <t>https://bellroute.cafe24.com/product/detail.html?product_no=41</t>
+  </si>
 </sst>
 </file>
 
@@ -602,12 +618,18 @@
       <name val="Malgun Gothic"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -628,7 +650,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -638,16 +660,19 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -913,91 +938,91 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" ht="15.0" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2"/>
-    </row>
-    <row r="2" ht="15.0" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>12</v>
+      <c r="C2" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>23</v>
+      <c r="C3" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>30</v>
+      <c r="C4" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>38</v>
+      <c r="C5" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" ht="15.0" customHeight="1">
+      <c r="A7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" ht="15.0" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>58</v>
+      <c r="C7" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>65</v>
+      <c r="C8" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="D8" s="2"/>
     </row>
@@ -6991,18 +7016,18 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" ht="17.25" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>112</v>
+      <c r="C2" s="4" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -12027,95 +12052,95 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" ht="17.25" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
+      <c r="A2" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>16</v>
+      <c r="C2" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>20</v>
+      <c r="C3" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>31</v>
+      <c r="C4" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>35</v>
+      <c r="C5" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>44</v>
+      <c r="C6" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>53</v>
+      <c r="C7" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>59</v>
+      <c r="C8" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>62</v>
+      <c r="C9" s="4" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -12125,7 +12150,7 @@
       <c r="B10" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>68</v>
       </c>
     </row>
@@ -12136,7 +12161,7 @@
       <c r="B11" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>71</v>
       </c>
     </row>
@@ -12147,7 +12172,7 @@
       <c r="B12" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>74</v>
       </c>
     </row>
@@ -12158,7 +12183,7 @@
       <c r="B13" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>77</v>
       </c>
     </row>
@@ -12169,7 +12194,7 @@
       <c r="B14" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>80</v>
       </c>
     </row>
@@ -12180,7 +12205,7 @@
       <c r="B15" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>83</v>
       </c>
     </row>
@@ -17111,25 +17136,26 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="C2"/>
-    <hyperlink r:id="rId2" ref="C3"/>
-    <hyperlink r:id="rId3" ref="C4"/>
-    <hyperlink r:id="rId4" ref="C5"/>
-    <hyperlink r:id="rId5" ref="C6"/>
-    <hyperlink r:id="rId6" ref="C7"/>
-    <hyperlink r:id="rId7" ref="C8"/>
-    <hyperlink r:id="rId8" ref="C9"/>
-    <hyperlink r:id="rId9" ref="C10"/>
-    <hyperlink r:id="rId10" ref="C11"/>
-    <hyperlink r:id="rId11" ref="C12"/>
-    <hyperlink r:id="rId12" ref="C13"/>
-    <hyperlink r:id="rId13" ref="C14"/>
-    <hyperlink r:id="rId14" ref="C15"/>
+    <hyperlink r:id="rId2" ref="C2"/>
+    <hyperlink r:id="rId3" ref="C3"/>
+    <hyperlink r:id="rId4" ref="C4"/>
+    <hyperlink r:id="rId5" ref="C5"/>
+    <hyperlink r:id="rId6" ref="C6"/>
+    <hyperlink r:id="rId7" ref="C7"/>
+    <hyperlink r:id="rId8" ref="C8"/>
+    <hyperlink r:id="rId9" ref="C9"/>
+    <hyperlink r:id="rId10" ref="C10"/>
+    <hyperlink r:id="rId11" ref="C11"/>
+    <hyperlink r:id="rId12" ref="C12"/>
+    <hyperlink r:id="rId13" ref="C13"/>
+    <hyperlink r:id="rId14" ref="C14"/>
+    <hyperlink r:id="rId15" ref="C15"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId15"/>
+  <drawing r:id="rId16"/>
+  <legacyDrawing r:id="rId17"/>
 </worksheet>
 </file>
 
@@ -17154,51 +17180,51 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" ht="17.25" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>17</v>
+      <c r="C2" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" ht="17.25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" ht="17.25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
     <row r="5" ht="17.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>50</v>
+      <c r="C5" s="4" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -22211,18 +22237,18 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" ht="17.25" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>13</v>
+      <c r="C2" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -27255,21 +27281,21 @@
         <v>85</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" s="3" t="s">
         <v>87</v>
       </c>
+      <c r="C2" s="4" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>94</v>
+      <c r="C3" s="4" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
@@ -32290,7 +32316,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" ht="17.25" customHeight="1">
@@ -32300,19 +32326,19 @@
       <c r="B2" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>97</v>
+      <c r="C3" s="4" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
@@ -32322,43 +32348,43 @@
       <c r="B4" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="6"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7"/>
     </row>
     <row r="6" ht="17.25" customHeight="1">
       <c r="A6" s="2"/>
@@ -38398,7 +38424,7 @@
       <c r="B2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>107</v>
       </c>
     </row>
@@ -43424,95 +43450,95 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="2" ht="17.25" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="C2" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" ht="17.25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="4" ht="17.25" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="3" ht="17.25" customHeight="1">
-      <c r="A3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C3" s="3" t="s">
+    </row>
+    <row r="5" ht="17.25" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="4" ht="17.25" customHeight="1">
-      <c r="A4" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C4" s="3" t="s">
+    </row>
+    <row r="6" ht="17.25" customHeight="1">
+      <c r="A6" s="2" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="5" ht="17.25" customHeight="1">
-      <c r="A5" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="3" t="s">
+    </row>
+    <row r="7" ht="17.25" customHeight="1">
+      <c r="A7" s="2" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="6" ht="17.25" customHeight="1">
-      <c r="A6" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C6" s="3" t="s">
+    </row>
+    <row r="8" ht="17.25" customHeight="1">
+      <c r="A8" s="2" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="7" ht="17.25" customHeight="1">
-      <c r="A7" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C8" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C7" s="3" t="s">
+    </row>
+    <row r="9" ht="17.25" customHeight="1">
+      <c r="A9" s="2" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="8" ht="17.25" customHeight="1">
-      <c r="A8" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C9" s="4" t="s">
         <v>132</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="9" ht="17.25" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
